--- a/Outputs/Recycling_Plot_Data/Repeal/02_National_Stacked_2050_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/02_National_Stacked_2050_data_Repeal.xlsx
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.5845245226777597</v>
+        <v>0.584029460298372</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.3202281559953118</v>
+        <v>0.3199556844246506</v>
       </c>
     </row>
     <row r="6">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>1.094560404406895</v>
+        <v>1.093633367717815</v>
       </c>
     </row>
     <row r="7">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.599648169289783</v>
+        <v>0.5991379484504484</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0676166079199273</v>
+        <v>0.06755934011078625</v>
       </c>
     </row>
     <row r="15">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.03704334177403395</v>
+        <v>0.03701182281691933</v>
       </c>
     </row>
     <row r="16">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.5477544793648994</v>
+        <v>0.5476838187546399</v>
       </c>
     </row>
     <row r="19">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.3290045456851686</v>
+        <v>0.3289610509363398</v>
       </c>
     </row>
     <row r="20">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>9.584875498766218</v>
+        <v>9.576026621080743</v>
       </c>
     </row>
     <row r="23">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>5.271311428760473</v>
+        <v>5.266441198862314</v>
       </c>
     </row>
     <row r="24">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>9.775939940225046</v>
+        <v>9.767660219016111</v>
       </c>
     </row>
     <row r="25">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>5.355688424906347</v>
+        <v>5.351131446359068</v>
       </c>
     </row>
     <row r="26">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>5.488690802098447</v>
+        <v>5.48404216166885</v>
       </c>
     </row>
     <row r="27">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>3.006945416648283</v>
+        <v>3.004386906020072</v>
       </c>
     </row>
     <row r="28">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>4.974707959637392</v>
+        <v>4.967049474693764</v>
       </c>
     </row>
     <row r="29">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>2.982401498978403</v>
+        <v>2.977285247541354</v>
       </c>
     </row>
     <row r="30">
